--- a/data.mn/public/datasets/mrpam-mining-permits.xlsx
+++ b/data.mn/public/datasets/mrpam-mining-permits.xlsx
@@ -1,19 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data EN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Өгөгдөл MN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data EN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Өгөгдөл MN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data EN'!$A$1:$I$1453</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Өгөгдөл MN'!$A$1:$I$1453</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -417,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1453"/>
+  <dimension ref="A1:I1475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -45490,8 +45487,689 @@
         <v>210.6</v>
       </c>
     </row>
+    <row r="1454">
+      <c r="A1454" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Arkhangai</t>
+        </is>
+      </c>
+      <c r="D1454" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1454" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H1454" t="n">
+        <v>11</v>
+      </c>
+      <c r="I1454" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1455" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Bayan-Ulgii</t>
+        </is>
+      </c>
+      <c r="D1455" t="n">
+        <v>116</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1455" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H1455" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1455" t="n">
+        <v>414.4</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Bayankhongor</t>
+        </is>
+      </c>
+      <c r="D1456" t="n">
+        <v>154</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>490.7</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>167</v>
+      </c>
+      <c r="H1456" t="n">
+        <v>55</v>
+      </c>
+      <c r="I1456" t="n">
+        <v>323.7</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Bulgan</t>
+        </is>
+      </c>
+      <c r="D1457" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>206.1</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H1457" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1457" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Darkhan-Uul</t>
+        </is>
+      </c>
+      <c r="D1458" t="n">
+        <v>67</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>60</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H1458" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1458" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Dornod</t>
+        </is>
+      </c>
+      <c r="D1459" t="n">
+        <v>170</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>680.9</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>82</v>
+      </c>
+      <c r="H1459" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1459" t="n">
+        <v>598.8</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1460" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Dornogovi</t>
+        </is>
+      </c>
+      <c r="D1460" t="n">
+        <v>373</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>1179.6</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>232</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>300.8</v>
+      </c>
+      <c r="H1460" t="n">
+        <v>141</v>
+      </c>
+      <c r="I1460" t="n">
+        <v>878.9</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1461" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Dundgovi</t>
+        </is>
+      </c>
+      <c r="D1461" t="n">
+        <v>193</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>472.9</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>135</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>224.3</v>
+      </c>
+      <c r="H1461" t="n">
+        <v>58</v>
+      </c>
+      <c r="I1461" t="n">
+        <v>248.7</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Govi-Altai</t>
+        </is>
+      </c>
+      <c r="D1462" t="n">
+        <v>139</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>654.3</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H1462" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1462" t="n">
+        <v>575.2</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1463" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>Govisumber</t>
+        </is>
+      </c>
+      <c r="D1463" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H1463" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1463" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1464" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Khentii</t>
+        </is>
+      </c>
+      <c r="D1464" t="n">
+        <v>236</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>272.2</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="H1464" t="n">
+        <v>99</v>
+      </c>
+      <c r="I1464" t="n">
+        <v>210.1</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Khovd</t>
+        </is>
+      </c>
+      <c r="D1465" t="n">
+        <v>122</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>427.9</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H1465" t="n">
+        <v>84</v>
+      </c>
+      <c r="I1465" t="n">
+        <v>395.6</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Khuvsgul</t>
+        </is>
+      </c>
+      <c r="D1466" t="n">
+        <v>22</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H1466" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1466" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Orkhon</t>
+        </is>
+      </c>
+      <c r="D1467" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H1467" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1467" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Selenge</t>
+        </is>
+      </c>
+      <c r="D1468" t="n">
+        <v>167</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>129</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H1468" t="n">
+        <v>38</v>
+      </c>
+      <c r="I1468" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>Sukhbaatar</t>
+        </is>
+      </c>
+      <c r="D1469" t="n">
+        <v>114</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>473.5</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>73</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="H1469" t="n">
+        <v>41</v>
+      </c>
+      <c r="I1469" t="n">
+        <v>411.9</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Tuv</t>
+        </is>
+      </c>
+      <c r="D1470" t="n">
+        <v>391</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>173.9</v>
+      </c>
+      <c r="H1470" t="n">
+        <v>91</v>
+      </c>
+      <c r="I1470" t="n">
+        <v>212.9</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1471" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Ulaanbaatar</t>
+        </is>
+      </c>
+      <c r="D1471" t="n">
+        <v>94</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H1471" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1471" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1472" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Umnugovi</t>
+        </is>
+      </c>
+      <c r="D1472" t="n">
+        <v>155</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>837.5</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>111</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="H1472" t="n">
+        <v>44</v>
+      </c>
+      <c r="I1472" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Uvs</t>
+        </is>
+      </c>
+      <c r="D1473" t="n">
+        <v>121</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>255.1</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1473" t="n">
+        <v>71</v>
+      </c>
+      <c r="I1473" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Uvurkhangai</t>
+        </is>
+      </c>
+      <c r="D1474" t="n">
+        <v>67</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="H1474" t="n">
+        <v>36</v>
+      </c>
+      <c r="I1474" t="n">
+        <v>175.4</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1475" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Zavkhan</t>
+        </is>
+      </c>
+      <c r="D1475" t="n">
+        <v>50</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>36</v>
+      </c>
+      <c r="I1475" t="n">
+        <v>210.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1453"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45502,7 +46180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1453"/>
+  <dimension ref="A1:I1475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -90575,8 +91253,689 @@
         <v>349</v>
       </c>
     </row>
+    <row r="1454">
+      <c r="A1454" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Архангай</t>
+        </is>
+      </c>
+      <c r="D1454" t="n">
+        <v>32</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>21</v>
+      </c>
+      <c r="G1454" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H1454" t="n">
+        <v>11</v>
+      </c>
+      <c r="I1454" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1455" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Баян-Өлгий</t>
+        </is>
+      </c>
+      <c r="D1455" t="n">
+        <v>116</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>434.7</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1455" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H1455" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1455" t="n">
+        <v>414.4</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Баянхонгор</t>
+        </is>
+      </c>
+      <c r="D1456" t="n">
+        <v>154</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>490.7</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>99</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>167</v>
+      </c>
+      <c r="H1456" t="n">
+        <v>55</v>
+      </c>
+      <c r="I1456" t="n">
+        <v>323.7</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Булган</t>
+        </is>
+      </c>
+      <c r="D1457" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>206.1</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H1457" t="n">
+        <v>35</v>
+      </c>
+      <c r="I1457" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Говь-Алтай</t>
+        </is>
+      </c>
+      <c r="D1458" t="n">
+        <v>139</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>654.3</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>54</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H1458" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1458" t="n">
+        <v>575.2</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Говьсүмбэр</t>
+        </is>
+      </c>
+      <c r="D1459" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H1459" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1459" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1460" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Дархан-Уул</t>
+        </is>
+      </c>
+      <c r="D1460" t="n">
+        <v>67</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>60</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H1460" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1460" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1461" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Дорноговь</t>
+        </is>
+      </c>
+      <c r="D1461" t="n">
+        <v>373</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>1179.6</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>232</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>300.8</v>
+      </c>
+      <c r="H1461" t="n">
+        <v>141</v>
+      </c>
+      <c r="I1461" t="n">
+        <v>878.9</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Дорнод</t>
+        </is>
+      </c>
+      <c r="D1462" t="n">
+        <v>170</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>680.9</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>85</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>82</v>
+      </c>
+      <c r="H1462" t="n">
+        <v>85</v>
+      </c>
+      <c r="I1462" t="n">
+        <v>598.8</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1463" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>Дундговь</t>
+        </is>
+      </c>
+      <c r="D1463" t="n">
+        <v>193</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>472.9</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>135</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>224.3</v>
+      </c>
+      <c r="H1463" t="n">
+        <v>58</v>
+      </c>
+      <c r="I1463" t="n">
+        <v>248.7</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1464" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Завхан</t>
+        </is>
+      </c>
+      <c r="D1464" t="n">
+        <v>50</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H1464" t="n">
+        <v>36</v>
+      </c>
+      <c r="I1464" t="n">
+        <v>210.6</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Орхон</t>
+        </is>
+      </c>
+      <c r="D1465" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H1465" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1465" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Сэлэнгэ</t>
+        </is>
+      </c>
+      <c r="D1466" t="n">
+        <v>167</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>129</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H1466" t="n">
+        <v>38</v>
+      </c>
+      <c r="I1466" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Сүхбаатар</t>
+        </is>
+      </c>
+      <c r="D1467" t="n">
+        <v>114</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>473.5</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>73</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="H1467" t="n">
+        <v>41</v>
+      </c>
+      <c r="I1467" t="n">
+        <v>411.9</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Төв</t>
+        </is>
+      </c>
+      <c r="D1468" t="n">
+        <v>391</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>173.9</v>
+      </c>
+      <c r="H1468" t="n">
+        <v>91</v>
+      </c>
+      <c r="I1468" t="n">
+        <v>212.9</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>Увс</t>
+        </is>
+      </c>
+      <c r="D1469" t="n">
+        <v>121</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>255.1</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1469" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1469" t="n">
+        <v>71</v>
+      </c>
+      <c r="I1469" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Улаанбаатар</t>
+        </is>
+      </c>
+      <c r="D1470" t="n">
+        <v>94</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>93</v>
+      </c>
+      <c r="G1470" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H1470" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1470" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1471" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Ховд</t>
+        </is>
+      </c>
+      <c r="D1471" t="n">
+        <v>122</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>427.9</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1471" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H1471" t="n">
+        <v>84</v>
+      </c>
+      <c r="I1471" t="n">
+        <v>395.6</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1472" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Хэнтий</t>
+        </is>
+      </c>
+      <c r="D1472" t="n">
+        <v>236</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>272.2</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>137</v>
+      </c>
+      <c r="G1472" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="H1472" t="n">
+        <v>99</v>
+      </c>
+      <c r="I1472" t="n">
+        <v>210.1</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Хөвсгөл</t>
+        </is>
+      </c>
+      <c r="D1473" t="n">
+        <v>22</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H1473" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1473" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Өвөрхангай</t>
+        </is>
+      </c>
+      <c r="D1474" t="n">
+        <v>67</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="H1474" t="n">
+        <v>36</v>
+      </c>
+      <c r="I1474" t="n">
+        <v>175.4</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1475" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Өмнөговь</t>
+        </is>
+      </c>
+      <c r="D1475" t="n">
+        <v>155</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>837.5</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>111</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>488.5</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>44</v>
+      </c>
+      <c r="I1475" t="n">
+        <v>349</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1453"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>